--- a/Du_Lieu_Mau_He_Thong/Theo_Phan_He/Lai_Suat/lai_suat_tiet_kiem_ca_nhan_tai_quay.xlsx
+++ b/Du_Lieu_Mau_He_Thong/Theo_Phan_He/Lai_Suat/lai_suat_tiet_kiem_ca_nhan_tai_quay.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InterestRates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LaiSuat" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -33,10 +35,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000843D"/>
         <bgColor rgb="0000843D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F9F5"/>
+        <bgColor rgb="00F4F9F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +93,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,173 +475,189 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>productCode</t>
+          <t>Mã sản phẩm / Gói lãi suất</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>termMonths</t>
+          <t>Kỳ hạn áp dụng (tháng)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ratePercentage</t>
+          <t>Mức lãi suất (%/năm)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>effectiveDate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Ngày hiệu lực</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_1M</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_3M</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_6M</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>3.3</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_9M</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_12M</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_24M</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>5.2</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_36M</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>SAVING_COUNTER_60M</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>5.2</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
